--- a/FPPN_Verification_coherence_20261023.xlsx
+++ b/FPPN_Verification_coherence_20261023.xlsx
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1430,32 +1430,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Provisions figées</t>
+          <t>Excédent par risque</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>106, 109, 222</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Montants identiques depuis le report à nouveau du 01/09/2020 : 2 867 602 878 FCFA et 1 961 695 412 FCFA. Seul mouvement : reclassement de 2024. Concorde avec le chef comptable (montants hérités d'environ 2004).</t>
+          <t>« Frais attribués au prorata des cotisations » sans dire quels comptes forment les frais, et clé de 70 % pour la maladie présentée comme à confirmer par un barème.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Questions 2 et 23 fusionnées. Constat inchangé.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Faible</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+          <t>Frais définis comme les charges de fonctionnement (comptes 612, 613, 618, 62 à 68). Clé de 70 % fondée sur les statuts (art. 17 : 3,5 % sur 5 %).</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Anomalie corrigée</t>
         </is>
       </c>
     </row>
@@ -1465,22 +1465,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Sigle CMP</t>
+          <t>Provisions figées</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Toutes</t>
+          <t>106, 109, 222</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>« Centre Médical du Policier (rapport de gestion 2023) ».</t>
+          <t>Montants identiques depuis le report à nouveau du 01/09/2020 : 2 867 602 878 FCFA et 1 961 695 412 FCFA. Seul mouvement : reclassement de 2024. Concorde avec le chef comptable (montants hérités d'environ 2004).</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Remplacé par « Clinique médicale du policier ».</t>
+          <t>Questions 2 et 23 fusionnées. Constat inchangé.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1488,9 +1488,9 @@
           <t>Faible</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Anomalie corrigée</t>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
     </row>
@@ -1500,27 +1500,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Formulations non établies</t>
+          <t>Sigle CMP</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>25, 26, 39, 56, 75, 80, 116, 119, 128, 129, 134, 191, 220, 222</t>
+          <t>Toutes</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>« À confirmer », « à préciser », « en principe », « probablement », « correspondraient ».</t>
+          <t>« Centre Médical du Policier (rapport de gestion 2023) ».</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Chaque phrase est réécrite sur le document ou le calcul qui l'établit. Ce qui manque est demandé au FPPN (liste des éléments à obtenir).</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Moyen</t>
+          <t>Remplacé par « Clinique médicale du policier ».</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Faible</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -1535,85 +1535,120 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Formulations non établies</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>25, 26, 39, 56, 75, 80, 116, 119, 128, 129, 134, 191, 220, 222</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>« À confirmer », « à préciser », « en principe », « probablement », « correspondraient ».</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Chaque phrase est réécrite sur le document ou le calcul qui l'établit. Ce qui manque est demandé au FPPN (liste des éléments à obtenir).</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Anomalie corrigée</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Points à clarifier</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>220, 222</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Questions déjà résolues par les documents : types de prêts (8 types dans les fichiers de production), barème des officiers (1 600 000 FCFA, cartographie des risques), compte de la provision décès (41591000), canal des fichiers retour.</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Questions retirées.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Faible</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Anomalie corrigée</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Code couleur : gravité</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Critique</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Change un verdict ou un chiffre clé du résumé exécutif.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="10" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Élevé</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Change un chiffre ou une conclusion d'une partie.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Moyen</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Précision ou cohérence entre diapositives.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Faible</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Forme ou formulation.</t>
         </is>
@@ -30553,7 +30588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comptes 5221 (DAT), 5330 (FCP) et 77 (produits financiers). Pour 2026, moyenne calculée sur l'année entière à partir des écritures du 01/01 au 31/08/2026.</t>
+          <t>Comptes 5221 (DAT), 5330 (FCP) et 77 (produits financiers). Pour 2026, moyenne calculée du 01/01 au 31/08/2026.</t>
         </is>
       </c>
     </row>
@@ -30789,7 +30824,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>327194871</v>
+        <v>247695588</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>485541804</v>
@@ -30804,7 +30839,7 @@
         <v>500000000</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>827194871</v>
+        <v>747695588</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>985541804</v>

--- a/FPPN_Verification_coherence_20261023.xlsx
+++ b/FPPN_Verification_coherence_20261023.xlsx
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1465,32 +1465,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Provisions figées</t>
+          <t>Tableau de bord (2/4) : risques longs</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>106, 109, 222</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Montants identiques depuis le report à nouveau du 01/09/2020 : 2 867 602 878 FCFA et 1 961 695 412 FCFA. Seul mouvement : reclassement de 2024. Concorde avec le chef comptable (montants hérités d'environ 2004).</t>
+          <t>Taux brut de rentabilité des placements calculé sur la moyenne des soldes de clôture (22,88 % en 2025), alors que la partie 9 publie le rendement lu dans les grands livres (15,44 % en 2025).</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Questions 2 et 23 fusionnées. Constat inchangé.</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Faible</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+          <t>Ratio recalculé sur l'encours moyen lu dans les grands livres, de 4,62 % en 2021 à 15,44 % en 2025, comme la partie 9 et le classeur des calculs.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Élevé</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Erreur corrigée</t>
         </is>
       </c>
     </row>
@@ -1500,27 +1500,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Sigle CMP</t>
+          <t>Références et sources</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Toutes</t>
+          <t>228, 268</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>« Centre Médical du Policier (rapport de gestion 2023) ».</t>
+          <t>Provision pour sinistres tardifs rattachée à l'article 334-8 du Code CIMA. La circulaire n° 00230/CIMA/CRCA/PDT/2005, lue dans l'extrait du Code CIMA reçu le 23/10/2026, la rattache à l'article 334-12.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Remplacé par « Clinique médicale du policier ».</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Faible</t>
+          <t>Référence corrigée (article 334-12). L'article 334-8 cité pour la santé des retraités est surligné jusqu'à lecture du texte (pages du Code CIMA illisibles dans l'envoi).</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Formulations non établies</t>
+          <t>Conformité prudentielle en bref</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>25, 26, 39, 56, 75, 80, 116, 119, 128, 129, 134, 191, 220, 222</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>« À confirmer », « à préciser », « en principe », « probablement », « correspondraient ».</t>
+          <t>« Retraité » désignait à la fois les policiers à la retraite et la lecture corrigée des comptes. Résumé exécutif limité à 2025.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Chaque phrase est réécrite sur le document ou le calcul qui l'établit. Ce qui manque est demandé au FPPN (liste des éléments à obtenir).</t>
+          <t>La lecture corrigée devient « lecture corrigée selon le PCMS », définie sur la diapositive. Matrice de 2020 au 31/08/2026, valeur et boule dans chaque case.</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1570,85 +1570,190 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>Provisions figées</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>106, 109, 222</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Montants identiques depuis le report à nouveau du 01/09/2020 : 2 867 602 878 FCFA et 1 961 695 412 FCFA. Seul mouvement : reclassement de 2024. Concorde avec le chef comptable (montants hérités d'environ 2004).</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Questions 2 et 23 fusionnées. Constat inchangé.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Sigle CMP</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>« Centre Médical du Policier (rapport de gestion 2023) ».</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Remplacé par « Clinique médicale du policier ».</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Anomalie corrigée</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Formulations non établies</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>25, 26, 39, 56, 75, 80, 116, 119, 128, 129, 134, 191, 220, 222</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>« À confirmer », « à préciser », « en principe », « probablement », « correspondraient ».</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Chaque phrase est réécrite sur le document ou le calcul qui l'établit. Ce qui manque est demandé au FPPN (liste des éléments à obtenir).</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Anomalie corrigée</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>Points à clarifier</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>220, 222</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Questions déjà résolues par les documents : types de prêts (8 types dans les fichiers de production), barème des officiers (1 600 000 FCFA, cartographie des risques), compte de la provision décès (41591000), canal des fichiers retour.</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Questions retirées.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Faible</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Anomalie corrigée</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Code couleur : gravité</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Critique</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Change un verdict ou un chiffre clé du résumé exécutif.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="10" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Élevé</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Change un chiffre ou une conclusion d'une partie.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Moyen</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Précision ou cohérence entre diapositives.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Faible</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Forme ou formulation.</t>
         </is>
